--- a/price-radar.xlsx
+++ b/price-radar.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 Instruções" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concorrentes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análise" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Battlecards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico de Preços" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo Features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto em Deals" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Monitoramento" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00e67e22"/>
+        <fgColor rgb="002e86c1"/>
       </patternFill>
     </fill>
   </fills>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PriceRadar — Inteligência Competitiva de Pricing para SaaS B2B</t>
+          <t>PriceRadar — Inteligência de Preços Competitivos</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>🎯 OBJETIVO: Detectar mudanças de preço dos concorrentes antes que impactem seus deals.</t>
+          <t>1. SETUP INICIAL: Na aba 'Checklist Monitoramento', cadastre seus concorrentes com URLs das páginas de pricing e defina frequência de verificação (semanal recomendado para concorrentes diretos).</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>📋 COMO USAR:</t>
+          <t>2. ROTINA SEMANAL: Visite cada pricing page na data agendada. Registre qualquer mudança na aba 'Histórico de Preços' com data, valor e fonte. Atualize o preço atual na aba 'Dashboard'.</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. ABA 'Concorrentes': Cadastre seus concorrentes e atualize preços semanalmente. Visite as páginas de pricing toda segunda-feira e atualize as colunas E (Preço Atual) e F (Preço Anterior). Fontes sugeridas: página de pricing, Wayback Machine (web.archive.org), propostas recebidas de prospects, G2/Capterra.</t>
+          <t>3. DASHBOARD: A aba principal mostra alertas automáticos — ⚠️ ALERTA para variações ≥10%, 👀 Observar para ≥5%. Revise os alertas semanalmente com seu time de Sales.</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2. ABA 'Histórico': Sempre que detectar uma mudança de preço, registre aqui com data, tipo e detalhes. Isso alimenta o Dashboard e a Análise automaticamente.</t>
+          <t>4. COMPARATIVO FEATURES: Atualize trimestralmente. O Score Total ponderado mostra sua posição competitiva real. Use nas reuniões de deal review.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. ABA 'Análise': Revise mensalmente. O Score de Ameaça (1-10) deve ser atualizado manualmente com base no impacto no seu pipeline. Fórmulas calculam diferenças e contam mudanças automaticamente.</t>
+          <t>5. IMPACTO EM DEALS: Registre todo deal onde um concorrente aparece. Isso gera dados para decidir quando ajustar seu pricing ou criar battlecards.</t>
         </is>
       </c>
     </row>
@@ -543,65 +543,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4. ABA 'Battlecards': Atualize após cada mudança de preço detectada. Distribua para o time de vendas. Cada linha é um script pronto para quando o prospect mencionar o concorrente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>5. ABA 'Dashboard': Visão executiva. Compartilhe com liderança. Atualiza automaticamente com dados das outras abas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>⏰ CADÊNCIA RECOMENDADA:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Semanal: Verificar preços dos concorrentes (15 min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>- Ao detectar mudança: Atualizar Histórico + Battlecard (20 min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- Mensal: Revisar Análise e Score de Ameaça (30 min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>- Trimestral: Avaliar se seu pricing precisa de ajuste (reunião de 1h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>💡 DICA PRO: Configure alertas no Visualping.io ou Distill.io para monitorar automaticamente as páginas de pricing dos concorrentes e receber notificações por email quando houver mudanças.</t>
+          <t>6. DICA PRO: Configure Google Alerts para '[concorrente] pricing' e 'novo plano'. Adicione capturas de tela do Archive.org como backup. Compartilhe a planilha com Sales para input em tempo real.</t>
         </is>
       </c>
     </row>
@@ -616,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -634,218 +576,554 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Métrica</t>
+          <t>Concorrente</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Valor Atual</t>
+          <t>Plano</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Variação 30d</t>
+          <t>Preço Atual (USD)</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Preço Anterior (USD)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Última Atualização</t>
+          <t>Variação (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Última Verificação</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Tendência 6M</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Concorrentes Monitorados</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>COUNTIF(Concorrentes!A2:A20,"&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>RivalCRM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>✅ Ativo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2">
+        <f>IFERROR((C2-D2)/D2*100,0)</f>
+        <v/>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H2">
+        <f>IF(ABS(E2)&gt;=10,"⚠️ ALERTA",IF(ABS(E2)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alterações de Preço (últimos 30d)</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>COUNTIFS(Histórico!F2:F100,"&gt;="&amp;TODAY()-30,Histórico!F2:F100,"&lt;="&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>B3-COUNTIFS(Histórico!F2:F100,"&gt;="&amp;TODAY()-60,Histórico!F2:F100,"&lt;"&amp;TODAY()-30)</f>
-        <v/>
+          <t>RivalCRM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>⚠️ Atenção</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3">
+        <f>IFERROR((C3-D3)/D3*100,0)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>↑ Alta</t>
+        </is>
+      </c>
+      <c r="H3">
+        <f>IF(ABS(E3)&gt;=10,"⚠️ ALERTA",IF(ABS(E3)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Seu Preço Médio (por seat/mês)</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R$ 89</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>IFERROR((C4-D4)/D4*100,0)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H4">
+        <f>IF(ABS(E4)&gt;=10,"⚠️ ALERTA",IF(ABS(E4)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Preço Médio do Mercado (por seat/mês)</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>IFERROR(TEXT(AVERAGE(Concorrentes!F2:F20),"R$ #.##0,00"),"—")</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>IFERROR(TEXT((AVERAGE(Concorrentes!F2:F20)-AVERAGE(Concorrentes!G2:G20))/AVERAGE(Concorrentes!G2:G20),"0,0%"),"—")</f>
-        <v/>
+          <t>PipelineHQ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>✅ Abaixo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>IFERROR((C5-D5)/D5*100,0)</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>↓ Baixa</t>
+        </is>
+      </c>
+      <c r="H5">
+        <f>IF(ABS(E5)&gt;=10,"⚠️ ALERTA",IF(ABS(E5)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Posição Competitiva (rank preço)</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>IFERROR(RANK(Concorrentes!F2,Concorrentes!F2:F20,1)&amp;"º mais barato","—")</f>
-        <v/>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>PipelineHQ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>✅ Competitivo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E6">
+        <f>IFERROR((C6-D6)/D6*100,0)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H6">
+        <f>IF(ABS(E6)&gt;=10,"⚠️ ALERTA",IF(ABS(E6)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deals Perdidos por Preço (mês)</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>⚠️ Atenção</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>IFERROR((C7-D7)/D7*100,0)</f>
+        <v/>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>↑ Alta</t>
+        </is>
+      </c>
+      <c r="H7">
+        <f>IF(ABS(E7)&gt;=10,"⚠️ ALERTA",IF(ABS(E7)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Win Rate vs Principal Concorrente</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>IFERROR(TEXT(VLOOKUP(MAX(Análise!H2:H20),Análise!H2:I20,2,FALSE),"YYYY-MM-DD"),"Definir")</f>
-        <v/>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3pp</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>✅ Subindo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>IFERROR((C8-D8)/D8*100,0)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H8">
+        <f>IF(ABS(E8)&gt;=10,"⚠️ ALERTA",IF(ABS(E8)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Próxima Revisão de Pricing Sugerida</t>
+          <t>DealFlow.io</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>📅 Agendada</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E9">
+        <f>IFERROR((C9-D9)/D9*100,0)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H9">
+        <f>IF(ABS(E9)&gt;=10,"⚠️ ALERTA",IF(ABS(E9)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E10">
+        <f>IFERROR((C10-D10)/D10*100,0)</f>
+        <v/>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>↑ Alta</t>
+        </is>
+      </c>
+      <c r="H10">
+        <f>IF(ABS(E10)&gt;=10,"⚠️ ALERTA",IF(ABS(E10)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>IFERROR((C11-D11)/D11*100,0)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>↓ Baixa</t>
+        </is>
+      </c>
+      <c r="H11">
+        <f>IF(ABS(E11)&gt;=10,"⚠️ ALERTA",IF(ABS(E11)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>IFERROR((C12-D12)/D12*100,0)</f>
+        <v/>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Estável</t>
+        </is>
+      </c>
+      <c r="H12">
+        <f>IF(ABS(E12)&gt;=10,"⚠️ ALERTA",IF(ABS(E12)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>IFERROR((C13-D13)/D13*100,0)</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>↑ Alta</t>
+        </is>
+      </c>
+      <c r="H13">
+        <f>IF(ABS(E13)&gt;=10,"⚠️ ALERTA",IF(ABS(E13)&gt;=5,"👀 Observar","✅ OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15">
+        <f>AVERAGE(C2:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16">
+        <f>COUNTIF(H2:H13,"⚠️ ALERTA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17">
+        <f>COUNTIF(H2:H13,"👀 Observar")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18">
+        <f>MAX(E2:E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19">
+        <f>MIN(E2:E13)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -858,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -876,196 +1154,143 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>Concorrente</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Plano Monitorado</t>
+          <t>Plano</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Modelo de Cobrança</t>
+          <t>Preço (USD)</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Preço Atual (seat/mês)</t>
+          <t>Modelo</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Preço Anterior</t>
+          <t>Billing Cycle</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Variação %</t>
+          <t>Fonte</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Features Incluídas</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Limite de Usuários</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Trial/Freemium</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Última Verificação</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Fonte</t>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Registros</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nós (ProdutoX)</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>produtox.com.br</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Per seat/mês</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>Per user/mês</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G2">
-        <f>IFERROR((F2-G2)/G2,0)</f>
-        <v/>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CRM + Automação + API</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Ilimitado</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14 dias trial</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Aumento de $10 vs mês anterior</t>
+        </is>
+      </c>
+      <c r="I2">
+        <f>COUNTIFS(B:B,B2,C:C,C2)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>alpha.io</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Per seat/mês</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>Per user/mês</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="G3">
-        <f>IFERROR((F3-G3)/G3,0)</f>
-        <v/>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CRM + Automação</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Página de pricing</t>
-        </is>
-      </c>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CompetitorBeta</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>beta.com</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1075,231 +1300,463 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Per seat/mês</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>Per user/mês</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>IFERROR((F4-G4)/G4,0)</f>
-        <v/>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CRM + Integrações</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>30 dias trial</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Página de pricing</t>
-        </is>
-      </c>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CompetitorGamma</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gamma.app</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Per seat/mês</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>Flat/mês</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="G5">
-        <f>IFERROR((F5-G5)/G5,0)</f>
-        <v/>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CRM + Automação + BI</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Wayback Machine</t>
+          <t>Reduziu de $25 — possível promoção</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CompetitorDelta</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delta.co</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Flat + seat</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>Flat/mês</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="G6">
-        <f>IFERROR((F6-G6)/G6,0)</f>
-        <v/>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CRM + Suporte Premium</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Demo only</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Proposta comercial</t>
-        </is>
-      </c>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CompetitorEpsilon</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>epsilon.io</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Per seat/mês</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Per user/mês</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G7">
-        <f>IFERROR((F7-G7)/G7,0)</f>
-        <v/>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CRM básico</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+          <t>Subiu $20 e adicionou features</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PipelineHQ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Per user/mês</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Flat/mês</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Aumento agressivo de 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Flat/mês</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Flat/mês</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Flat/mês</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Baixou preço — guerra de preço no entry level</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Flat/mês</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pricing page</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Página de pricing</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Per user/mês</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sales call</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Preço anual com desconto de 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Per user/mês</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Email mkt</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1312,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1330,563 +1787,491 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Concorrente</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Plano</t>
+          <t>Nosso Produto</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Preço Antigo</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Preço Novo</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Variação %</t>
+          <t>DealFlow.io</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Data da Mudança</t>
+          <t>CloserApp</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Tipo de Mudança</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Detalhes</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Impacto Estimado</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Ação Tomada</t>
+          <t>Peso Estratégico (1-5)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>CRM básico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="E2">
-        <f>IFERROR((D2-C2)/C2,0)</f>
-        <v/>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aumento de 10% no plano Business</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Alto - principal concorrente</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Reposicionar messaging</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CompetitorGamma</t>
+          <t>Pipeline visual</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E3">
-        <f>IFERROR((D3-C3)/C3,0)</f>
-        <v/>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Novo tier com BI incluído</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Destacar nosso BI gratuito</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CompetitorEpsilon</t>
+          <t>Automação de emails</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E4">
-        <f>IFERROR((D4-C4)/C4,0)</f>
-        <v/>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aumento geral +8,7%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Baixo - segmento diferente</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CompetitorBeta</t>
+          <t>Relatórios avançados</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E5">
-        <f>IFERROR((D5-C5)/C5,0)</f>
-        <v/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Redução</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Redução agressiva para ganhar mercado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Alto - undercut direto</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Revisar desconto volume</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>Integrações (Slack, Zapier)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6">
-        <f>IFERROR((D6-C6)/C6,0)</f>
-        <v/>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Lançamento de plano gratuito</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Alto - entrada de mercado</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Criar comparativo público</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CompetitorDelta</t>
+          <t>API aberta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="E7">
-        <f>IFERROR((D7-C7)/C7,0)</f>
-        <v/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Reajuste trimestral</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Baixo</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CompetitorGamma</t>
+          <t>Onboarding white-glove</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E8">
-        <f>IFERROR((D8-C8)/C8,0)</f>
-        <v/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Inclusão de novo módulo</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Atualizar battlecard</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>Mobile app nativo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E9">
-        <f>IFERROR((D9-C9)/C9,0)</f>
-        <v/>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Segundo aumento no ano</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Comunicar estabilidade do nosso preço</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CompetitorEpsilon</t>
+          <t>Multi-idioma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="E10">
-        <f>IFERROR((D10-C10)/C10,0)</f>
-        <v/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Reajuste anual</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Baixo</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CompetitorBeta</t>
+          <t>Score de lead (AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E11">
-        <f>IFERROR((D11-C11)/C11,0)</f>
-        <v/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aumento</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Aumento pós rodada de investimento</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Monitorar próximos movimentos</t>
-        </is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Preço plano comparável (Pro)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$59</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>$79</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>$59</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>$49</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>$45</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCORE TOTAL</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>SUMPRODUCT((B2:B10="✅")*1,G2:G10)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>SUMPRODUCT((C2:C10="✅")*1,G2:G10)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMPRODUCT((D2:D10="✅")*1,G2:G10)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMPRODUCT((E2:E10="✅")*1,G2:G10)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMPRODUCT((F2:F10="✅")*1,G2:G10)</f>
+        <v/>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14">
+        <f>COUNTIF(B2:B10,"✅")</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(C2:C10,"✅")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>COUNTIF(D2:D10,"✅")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(E2:E10,"✅")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>COUNTIF(F2:F10,"✅")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +2285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1918,338 +2303,478 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Concorrente</t>
+          <t>Deal</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Preço Atual</t>
+          <t>Valor (ARR)</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Preço/Feature Score</t>
+          <t>Concorrente no Deal</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Mudanças (12 meses)</t>
+          <t>Plano Concorrente</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Tendência</t>
+          <t>Preço Concorrente</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Diferença vs Nós (R$)</t>
+          <t>Nosso Preço</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Diferença vs Nós (%)</t>
+          <t>Delta (%)</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Score de Ameaça (1-10)</t>
+          <t>Status Deal</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Próxima Revisão Estimada</t>
+          <t>Ação Tomada</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Recomendação</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>Acme Corp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C2">
-        <f>IFERROR(B2/LEN(SUBSTITUTE(Concorrentes!H3," ","")),0)</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>COUNTIF(Histórico!A2:A100,A2)</f>
-        <v/>
+          <t>14400</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RivalCRM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>📈 Subindo</t>
-        </is>
-      </c>
-      <c r="F2">
-        <f>B2-Concorrentes!F2</f>
-        <v/>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="G2">
-        <f>IFERROR(F2/Concorrentes!F2,0)</f>
+        <f>IFERROR((F2-E2)/E2*100,0)</f>
         <v/>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Em negociação</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Manter preço; reforçar valor de API inclusa</t>
-        </is>
-      </c>
+          <t>Destacar ROI e features extras</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CompetitorBeta</t>
+          <t>Beta Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C3">
-        <f>IFERROR(B3/LEN(SUBSTITUTE(Concorrentes!H4," ","")),0)</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>COUNTIF(Histórico!A2:A100,A3)</f>
-        <v/>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PipelineHQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>📉 Descendo</t>
-        </is>
-      </c>
-      <c r="F3">
-        <f>B3-Concorrentes!F2</f>
-        <v/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="G3">
-        <f>IFERROR(F3/Concorrentes!F2,0)</f>
+        <f>IFERROR((F3-E3)/E3*100,0)</f>
         <v/>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Perdido</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>Preço não competitivo no entry</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALERTA: undercut ativo. Criar bundle competitivo</t>
+          <t>Criar plano Starter a $19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CompetitorGamma</t>
+          <t>Gama SA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C4">
-        <f>IFERROR(B4/LEN(SUBSTITUTE(Concorrentes!H5," ","")),0)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>COUNTIF(Histórico!A2:A100,A4)</f>
-        <v/>
+          <t>21600</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>📈 Subindo</t>
-        </is>
-      </c>
-      <c r="F4">
-        <f>B4-Concorrentes!F2</f>
-        <v/>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="G4">
-        <f>IFERROR(F4/Concorrentes!F2,0)</f>
+        <f>IFERROR((F4-E4)/E4*100,0)</f>
         <v/>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Ganho</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>Menor preço + melhor feature set</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sem ação. Tendência favorável</t>
+          <t>Fechado em 12 dias</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CompetitorDelta</t>
+          <t>Delta Inc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="C5">
-        <f>IFERROR(B5/LEN(SUBSTITUTE(Concorrentes!H6," ","")),0)</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>COUNTIF(Histórico!A2:A100,A5)</f>
-        <v/>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>➡️ Estável</t>
-        </is>
-      </c>
-      <c r="F5">
-        <f>B5-Concorrentes!F2</f>
-        <v/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="G5">
-        <f>IFERROR(F5/Concorrentes!F2,0)</f>
+        <f>IFERROR((F5-E5)/E5*100,0)</f>
         <v/>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Em negociação</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Baixa ameaça. Foco em diferenciação</t>
-        </is>
-      </c>
+          <t>Oferecer trial estendido 30d</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CompetitorEpsilon</t>
+          <t>Epsilon Co</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C6">
-        <f>IFERROR(B6/LEN(SUBSTITUTE(Concorrentes!H7," ","")),0)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>COUNTIF(Histórico!A2:A100,A6)</f>
-        <v/>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RivalCRM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>📈 Subindo</t>
-        </is>
-      </c>
-      <c r="F6">
-        <f>B6-Concorrentes!F2</f>
-        <v/>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="G6">
-        <f>IFERROR(F6/Concorrentes!F2,0)</f>
+        <f>IFERROR((F6-E6)/E6*100,0)</f>
         <v/>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ganho</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>Match de preço + onboarding grátis</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monitorar; se subir mais, destacar custo-benefício nosso</t>
+          <t>Upsell para anual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>— MÉDIA MERCADO —</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>AVERAGE(B2:B6)</f>
-        <v/>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7">
-        <f>AVERAGE(H2:H6)</f>
-        <v/>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Zeta Tech</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PipelineHQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G7">
+        <f>IFERROR((F7-E7)/E7*100,0)</f>
+        <v/>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Em negociação</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Preço muito abaixo — enfatizar valor</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>— MEDIANA MERCADO —</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>MEDIAN(B2:B6)</f>
-        <v/>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8">
-        <f>MEDIAN(H2:H6)</f>
-        <v/>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Eta Global</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DealFlow.io</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G8">
+        <f>IFERROR((F8-E8)/E8*100,0)</f>
+        <v/>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Proposta enviada</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Desconto 10% para anual</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Theta SaaS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CloserApp</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G9">
+        <f>IFERROR((F9-E9)/E9*100,0)</f>
+        <v/>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Perdido</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sem margem para desconto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Revisar pricing do plano Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10">
+        <f>SUM(B2:B9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>AVERAGE(E2:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>AVERAGE(F2:F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11">
+        <f>SUMIFS(B2:B9,H2:H9,"Ganho")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <f>SUMIFS(B2:B9,H2:H9,"Perdido")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13">
+        <f>IFERROR(B11/B10*100,0)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2262,7 +2787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2285,302 +2810,197 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Nosso Preço</t>
+          <t>URL Pricing Page</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>Preço Deles</t>
+          <t>Frequência Check</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>Economia p/ Cliente</t>
+          <t>Responsável</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>Pitch de 1 Linha</t>
+          <t>Último Check</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>Ponto Forte Deles</t>
+          <t>Próximo Check</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Nosso Contra-Argumento</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Objeção Comum</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>Resposta à Objeção</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>Última Atualização</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CompetitorAlpha</t>
+          <t>RivalCRM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R$ 89/seat</t>
+          <t>https://rivalcrm.com/pricing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R$ 109/seat</t>
-        </is>
-      </c>
-      <c r="D2">
-        <f>IFERROR(TEXT((VALUE(SUBSTITUTE(SUBSTITUTE(C2,"R$ ",""),"/seat",""))-VALUE(SUBSTITUTE(SUBSTITUTE(B2,"R$ ",""),"/seat","")))*10,"R$ #.##0/ano (10 seats)"),"—")</f>
-        <v/>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>João</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mesmas features por 18% menos, com API inclusa sem custo extra</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Brand recognition forte</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Nossos clientes crescem 2x mais rápido no onboarding</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>"Alpha é mais conhecida no mercado"</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Conhecida não significa melhor. Veja nosso NPS de 72 vs 54 deles.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="F2">
+        <f>E2+7</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>IF(TODAY()&gt;F2,"🔴 Atrasado",IF(TODAY()&gt;=F2-2,"🟡 Em breve","🟢 OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CompetitorBeta</t>
+          <t>PipelineHQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R$ 89/seat</t>
+          <t>https://pipelinehq.io/pricing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R$ 79/seat</t>
-        </is>
-      </c>
-      <c r="D3">
-        <f>IFERROR(TEXT((VALUE(SUBSTITUTE(SUBSTITUTE(B3,"R$ ",""),"/seat",""))-VALUE(SUBSTITUTE(SUBSTITUTE(C3,"R$ ",""),"/seat","")))*10*-1,"+R$ #.##0/ano (10 seats)"),"—")</f>
-        <v/>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>R$ 10 a mais que compra automação completa + API + usuários ilimitados</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Preço mais baixo do mercado</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Limite de 30 users e sem automação nativa. Custo real é maior.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>"Beta é mais barato"</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sem automação, você gasta +R$50/seat em Zapier. Custo total: R$129 vs nosso R$89.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="F3">
+        <f>E3+7</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(TODAY()&gt;F3,"🔴 Atrasado",IF(TODAY()&gt;=F3-2,"🟡 Em breve","🟢 OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CompetitorGamma</t>
+          <t>DealFlow.io</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R$ 89/seat</t>
+          <t>https://dealflow.io/plans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R$ 95/seat</t>
-        </is>
-      </c>
-      <c r="D4">
-        <f>IFERROR(TEXT((VALUE(SUBSTITUTE(SUBSTITUTE(C4,"R$ ",""),"/seat",""))-VALUE(SUBSTITUTE(SUBSTITUTE(B4,"R$ ",""),"/seat","")))*10,"R$ #.##0/ano (10 seats)"),"—")</f>
-        <v/>
+          <t>Quinzenal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>João</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BI nativo incluso no nosso plano, sem cobrar R$6/seat a mais</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Módulo de BI integrado</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Nosso BI é equivalente e incluso. Deles cobra separado abaixo de 50 seats.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>"Gamma tem BI melhor"</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Nosso BI cobre 95% dos casos. Para os 5% restantes, integramos com qualquer ferramenta via API.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="F4">
+        <f>E4+14</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(TODAY()&gt;F4,"🔴 Atrasado",IF(TODAY()&gt;=F4-2,"🟡 Em breve","🟢 OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CompetitorDelta</t>
+          <t>CloserApp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R$ 89/seat</t>
+          <t>https://closerapp.com/pricing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>R$ 115/seat</t>
-        </is>
-      </c>
-      <c r="D5">
-        <f>IFERROR(TEXT((VALUE(SUBSTITUTE(SUBSTITUTE(C5,"R$ ",""),"/seat",""))-VALUE(SUBSTITUTE(SUBSTITUTE(B5,"R$ ",""),"/seat","")))*10,"R$ #.##0/ano (10 seats)"),"—")</f>
-        <v/>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Economize 23% com suporte premium incluso em todos os planos</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Suporte white-glove dedicado</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Nosso suporte tem SLA de 2h em todos os planos, sem custo adicional.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>"Delta tem suporte melhor"</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Nosso SLA de 2h é garantido contratualmente. Delta cobra extra por SLA.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F5">
+        <f>E5+7</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(TODAY()&gt;F5,"🔴 Atrasado",IF(TODAY()&gt;=F5-2,"🟡 Em breve","🟢 OK"))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CompetitorEpsilon</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>R$ 89/seat</t>
-        </is>
-      </c>
+          <t>NovoConcorrente X</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R$ 75/seat</t>
-        </is>
-      </c>
-      <c r="D6">
-        <f>IFERROR(TEXT((VALUE(SUBSTITUTE(SUBSTITUTE(C6,"R$ ",""),"/seat",""))-VALUE(SUBSTITUTE(SUBSTITUTE(B6,"R$ ",""),"/seat","")))*10*-1,"+R$ #.##0/ano (10 seats)"),"—")</f>
-        <v/>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Plataforma completa vs CRM básico — o barato sai caro quando você escala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Entrada fácil com freemium</t>
-        </is>
-      </c>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>João</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Limite de 15 users. Migração forçada em 6 meses quando crescer.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>"Epsilon é de graça pra começar"</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Grátis até 15 users. Na migração, perdem dados e gastam 3 semanas. Começar certo custa R$14 a mais.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>🆕 Configurar</t>
         </is>
       </c>
     </row>
